--- a/application-layer-protocol/application-layer-protocol.xlsx
+++ b/application-layer-protocol/application-layer-protocol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67CCA69-F0DD-47D1-B5C0-116682239A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B717254-55A8-486F-AEE0-DB4813DECB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -68,9 +68,6 @@
     <t>dct:publisher</t>
   </si>
   <si>
-    <t>NAPCORE SubWG4.4</t>
-  </si>
-  <si>
     <t>dct:contributor</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>owl:deprecated^^xsd:boolean</t>
   </si>
   <si>
-    <t>dcterms:replacedBy</t>
-  </si>
-  <si>
     <t>skos:notation</t>
   </si>
   <si>
@@ -194,10 +188,19 @@
     <t>gRPC Remote Procedure Call (gRPC)</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>File Transfer Protocol (FTP/SFTP)</t>
+  </si>
+  <si>
+    <t>Ed Ooms (NDW)</t>
+  </si>
+  <si>
+    <t>dcterms:isReplacedBy</t>
+  </si>
+  <si>
+    <t>NAPCORE Task 4.4</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -334,6 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -643,7 +647,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="48.140625" customWidth="1"/>
     <col min="4" max="4" width="57.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="1" customWidth="1"/>
@@ -698,40 +702,43 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>46</v>
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="str">
         <f>_xlfn.CONCAT(B1,"/",B9)</f>
@@ -741,51 +748,51 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="10" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -794,7 +801,7 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/ots2</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12" t="b">
@@ -812,7 +819,7 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/ocit</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12" t="b">
@@ -830,10 +837,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/http-https</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12" t="b">
@@ -847,13 +854,13 @@
     </row>
     <row r="20" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -866,10 +873,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/sse</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" s="15" t="str">
         <f>A20</f>
@@ -885,10 +892,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/rest</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D22" s="15" t="str">
         <f>A20</f>
@@ -904,10 +911,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/long-polling</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" s="15" t="str">
         <f>A20</f>
@@ -923,21 +930,21 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/soap</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -946,10 +953,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/rss</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -958,10 +965,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/amqp</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -970,10 +977,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/mqtt</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -982,10 +989,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/grpc</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -994,10 +1001,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/zeromq</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1006,10 +1013,10 @@
         <v>https://w3id.org/mobilitydcat-ap/application-layer-protocol/other</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1027,14 +1034,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1239,21 +1244,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC6AC960-8266-4EB4-8874-7C8BE96E25EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
-    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1278,9 +1282,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC6AC960-8266-4EB4-8874-7C8BE96E25EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>